--- a/r4-ELGA-IV-Diabetes-main/ValueSet-fussdiagnose.xlsx
+++ b/r4-ELGA-IV-Diabetes-main/ValueSet-fussdiagnose.xlsx
@@ -7,13 +7,13 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include from SNOMED CT" r:id="rId4" sheetId="2"/>
+    <sheet name="Include #0" r:id="rId4" sheetId="2"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="36">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-29T09:18:44+00:00</t>
+    <t>2025-01-27T15:05:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,6 +72,12 @@
     <t>ELGA GmbH (https://www.elga.gv.at/)</t>
   </si>
   <si>
+    <t>Jurisdiction</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
     <t>Description</t>
   </si>
   <si>
@@ -109,9 +115,6 @@
   </si>
   <si>
     <t>HFpEF - heart failure with preserved ejection fraction</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>System URI</t>
@@ -251,7 +254,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -348,20 +351,28 @@
       <c r="A12" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="B12" s="2"/>
+      <c r="B12" t="s" s="2">
+        <v>22</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="B14" t="s" s="2">
         <v>24</v>
+      </c>
+      <c r="B14" s="2"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -380,50 +391,50 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/r4-ELGA-IV-Diabetes-main/ValueSet-fussdiagnose.xlsx
+++ b/r4-ELGA-IV-Diabetes-main/ValueSet-fussdiagnose.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.1.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-27T15:05:45+00:00</t>
+    <t>2025-01-30T07:29:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-IV-Diabetes-main/ValueSet-fussdiagnose.xlsx
+++ b/r4-ELGA-IV-Diabetes-main/ValueSet-fussdiagnose.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-30T07:29:10+00:00</t>
+    <t>2025-01-30T08:21:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-IV-Diabetes-main/ValueSet-fussdiagnose.xlsx
+++ b/r4-ELGA-IV-Diabetes-main/ValueSet-fussdiagnose.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="37">
   <si>
     <t>Property</t>
   </si>
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://diab.iv.elga.gv.at/ValueSet/fussdiagnose</t>
+    <t>https://fhir.hl7.at/elga-iv-diabetes-r4/ValueSet/fussdiagnose</t>
   </si>
   <si>
     <t>Version</t>
@@ -54,10 +54,13 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-30T08:21:10+00:00</t>
+    <t>2025-02-28T13:11:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -313,66 +316,68 @@
       <c r="A7" t="s" s="2">
         <v>12</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -391,50 +396,50 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/r4-ELGA-IV-Diabetes-main/ValueSet-fussdiagnose.xlsx
+++ b/r4-ELGA-IV-Diabetes-main/ValueSet-fussdiagnose.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-28T13:11:58+00:00</t>
+    <t>2025-02-28T14:02:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-IV-Diabetes-main/ValueSet-fussdiagnose.xlsx
+++ b/r4-ELGA-IV-Diabetes-main/ValueSet-fussdiagnose.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-28T14:02:02+00:00</t>
+    <t>2025-03-03T10:25:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
